--- a/ICD codes_malnutrition study.xlsx
+++ b/ICD codes_malnutrition study.xlsx
@@ -4949,8 +4949,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="dokument" ma:contentTypeID="0x0101000F48778665866F4D8347936C0218526D" ma:contentTypeVersion="10" ma:contentTypeDescription="Skapa ett nytt dokument." ma:contentTypeScope="" ma:versionID="ab4a38b194b5076c8637a23b79ea60b2">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8122317a-a166-4aca-8a73-cea3da482592" xmlns:ns3="4465cf7b-dff5-40ba-a744-c962d51df52a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="92410e981e4716dcb4e6d2ea79624fe2" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000F48778665866F4D8347936C0218526D" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b64786a3cf0087cf934c39799665206d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8122317a-a166-4aca-8a73-cea3da482592" xmlns:ns3="4465cf7b-dff5-40ba-a744-c962d51df52a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="548e74e36a28f42524e46a5b3754702e" ns2:_="" ns3:_="">
     <xsd:import namespace="8122317a-a166-4aca-8a73-cea3da482592"/>
     <xsd:import namespace="4465cf7b-dff5-40ba-a744-c962d51df52a"/>
     <xsd:element name="properties">
@@ -4998,7 +4998,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Bildmarkeringar" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d34d398b-60ba-4ad0-a6da-da1ce693b88b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d34d398b-60ba-4ad0-a6da-da1ce693b88b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -5047,8 +5047,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Innehållstyp"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Rubrik"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -5146,5 +5146,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13292C37-1F85-4071-B7B4-30F496D1AD3C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4817D2F5-18A6-4603-846D-2CE86865CE27}"/>
 </file>